--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="426">
   <si>
     <t>key</t>
   </si>
@@ -878,7 +878,7 @@
     <t>range</t>
   </si>
   <si>
-    <t>範圍</t>
+    <t>距離</t>
   </si>
   <si>
     <t>攻擊半徑</t>
@@ -1123,6 +1123,30 @@
     <t>灼燒</t>
   </si>
   <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>類型</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>單體</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>群體</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>範圍</t>
+  </si>
+  <si>
     <t>bleed</t>
   </si>
   <si>
@@ -1154,9 +1178,6 @@
   </si>
   <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>類型</t>
   </si>
   <si>
     <t>戰鬥類型</t>
@@ -2513,35 +2534,35 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2549,7 +2570,7 @@
         <v>254</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>257</v>
@@ -3325,7 +3346,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3809,6 +3830,38 @@
         <v>364</v>
       </c>
       <c r="C53" s="4"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>372</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3856,26 +3909,26 @@
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B4" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B6" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3926,18 +3979,18 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3950,29 +4003,29 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4025,42 +4078,42 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -4105,74 +4158,74 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B3" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B6" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B8" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B9" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B10" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B12" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="432">
   <si>
     <t>key</t>
   </si>
@@ -1193,6 +1193,24 @@
   </si>
   <si>
     <t>遠距</t>
+  </si>
+  <si>
+    <t>reqClass</t>
+  </si>
+  <si>
+    <t>需要裝備</t>
+  </si>
+  <si>
+    <t>sword</t>
+  </si>
+  <si>
+    <t>劍</t>
+  </si>
+  <si>
+    <t>bow</t>
+  </si>
+  <si>
+    <t>弓</t>
   </si>
   <si>
     <t>quest</t>
@@ -2534,35 +2552,35 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2570,7 +2588,7 @@
         <v>254</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>257</v>
@@ -3938,7 +3956,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="8.875" style="1" customWidth="1"/>
@@ -4020,13 +4038,56 @@
         <v>386</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>387</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>388</v>
       </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4078,42 +4139,42 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -4158,63 +4219,63 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B3" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B4" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B5" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B8" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B10" t="s">
         <v>378</v>
@@ -4222,10 +4283,10 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B12" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -1198,7 +1198,7 @@
     <t>reqClass</t>
   </si>
   <si>
-    <t>需要裝備</t>
+    <t>需求</t>
   </si>
   <si>
     <t>sword</t>
@@ -1801,7 +1801,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2404,7 +2405,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2622,7 +2624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
@@ -2934,7 +2936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
@@ -3168,7 +3170,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
       <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
@@ -4203,7 +4206,8 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.75" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="439">
   <si>
     <t>key</t>
   </si>
@@ -662,6 +662,18 @@
     <t>Wick</t>
   </si>
   <si>
+    <t>dummy</t>
+  </si>
+  <si>
+    <t>木樁</t>
+  </si>
+  <si>
+    <t>練習攻擊用</t>
+  </si>
+  <si>
+    <t>Training Dummy</t>
+  </si>
+  <si>
     <t>musk</t>
   </si>
   <si>
@@ -1322,6 +1334,15 @@
   </si>
   <si>
     <t>解剖</t>
+  </si>
+  <si>
+    <t>restore</t>
+  </si>
+  <si>
+    <t>恢復</t>
+  </si>
+  <si>
+    <t>Restore</t>
   </si>
 </sst>
 </file>
@@ -2383,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.375" style="1" customWidth="1"/>
@@ -2554,46 +2575,59 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>431</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -2624,7 +2658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
@@ -2936,7 +2970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
@@ -2964,91 +2998,102 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3057,10 +3102,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D12" s="8"/>
     </row>
@@ -3187,16 +3232,16 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -3204,72 +3249,72 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3408,57 +3453,57 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -3467,99 +3512,99 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C9" s="18"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>78</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3568,55 +3613,55 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
@@ -3625,46 +3670,46 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C26" s="18"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C27" s="18"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C28" s="18"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C29" s="18"/>
     </row>
@@ -3674,7 +3719,7 @@
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>71</v>
@@ -3685,24 +3730,24 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
@@ -3711,177 +3756,177 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C49" s="4"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C53" s="4"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3930,26 +3975,26 @@
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4000,18 +4045,18 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4024,29 +4069,29 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4061,10 +4106,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4072,10 +4117,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4083,10 +4128,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4142,42 +4187,42 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4223,74 +4268,74 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B5" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B9" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B12" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="446">
   <si>
     <t>key</t>
   </si>
@@ -752,6 +752,21 @@
     <t>盜賊</t>
   </si>
   <si>
+    <t>guard-1</t>
+  </si>
+  <si>
+    <t>守衛</t>
+  </si>
+  <si>
+    <t>駐守南門的守衛，跟搭檔輪流日夜巡邏村子</t>
+  </si>
+  <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>guard-2</t>
+  </si>
+  <si>
     <t>ranger</t>
   </si>
   <si>
@@ -822,6 +837,12 @@
   </si>
   <si>
     <t>Merchant</t>
+  </si>
+  <si>
+    <t>guard</t>
+  </si>
+  <si>
+    <t>巡邏村莊、維持治安。</t>
   </si>
   <si>
     <t>str</t>
@@ -2575,59 +2596,59 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -2970,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
@@ -3100,22 +3121,46 @@
       <c r="A11" s="7"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>240</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>241</v>
       </c>
+      <c r="C12" s="9"/>
       <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
@@ -3232,16 +3277,16 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -3249,77 +3294,89 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="D10" s="8"/>
+        <v>270</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
@@ -3453,57 +3510,57 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -3512,99 +3569,99 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C9" s="18"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>78</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3613,55 +3670,55 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
@@ -3670,46 +3727,46 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C26" s="18"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C27" s="18"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C28" s="18"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C29" s="18"/>
     </row>
@@ -3719,7 +3776,7 @@
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>71</v>
@@ -3730,24 +3787,24 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
@@ -3756,177 +3813,177 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B40" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>340</v>
-      </c>
       <c r="C40" s="19" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C49" s="4"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C53" s="4"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -3975,26 +4032,26 @@
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B5" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B6" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -4045,18 +4102,18 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4069,29 +4126,29 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4106,10 +4163,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4117,10 +4174,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4128,10 +4185,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4187,42 +4244,42 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -4268,74 +4325,74 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B5" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B6" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B8" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B10" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B12" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -28,10 +28,10 @@
     <t>key</t>
   </si>
   <si>
-    <t>tw</t>
-  </si>
-  <si>
-    <t>us</t>
+    <t>zh-TW</t>
+  </si>
+  <si>
+    <t>en</t>
   </si>
   <si>
     <t>lab</t>
@@ -2991,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -23,15 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="361">
   <si>
     <t>key</t>
   </si>
   <si>
-    <t>zh-TW</t>
-  </si>
-  <si>
-    <t>en</t>
+    <t>text</t>
   </si>
   <si>
     <t>lab</t>
@@ -49,12 +46,6 @@
     <t>攻擊用</t>
   </si>
   <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
     <t>分類</t>
   </si>
   <si>
@@ -64,175 +55,115 @@
     <t>防具</t>
   </si>
   <si>
-    <t>Armor</t>
-  </si>
-  <si>
     <t>item</t>
   </si>
   <si>
     <t>道具</t>
   </si>
   <si>
-    <t>Item</t>
-  </si>
-  <si>
     <t>skill</t>
   </si>
   <si>
     <t>技能</t>
   </si>
   <si>
-    <t>Skill</t>
-  </si>
-  <si>
     <t>ability</t>
   </si>
   <si>
     <t>能力</t>
   </si>
   <si>
-    <t>Ability</t>
-  </si>
-  <si>
     <t>helmet</t>
   </si>
   <si>
     <t>頭盔</t>
   </si>
   <si>
-    <t>Helmet</t>
-  </si>
-  <si>
     <t>chestplate</t>
   </si>
   <si>
     <t>胸甲</t>
   </si>
   <si>
-    <t>Chestplate</t>
-  </si>
-  <si>
     <t>gloves</t>
   </si>
   <si>
     <t>手套</t>
   </si>
   <si>
-    <t>Gloves</t>
-  </si>
-  <si>
     <t>boots</t>
   </si>
   <si>
     <t>靴子</t>
   </si>
   <si>
-    <t>Boots</t>
-  </si>
-  <si>
     <t>necklace</t>
   </si>
   <si>
     <t>項鍊</t>
   </si>
   <si>
-    <t>Necklace</t>
-  </si>
-  <si>
     <t>ring</t>
   </si>
   <si>
     <t>戒子</t>
   </si>
   <si>
-    <t>Ring</t>
-  </si>
-  <si>
     <t>bag</t>
   </si>
   <si>
     <t>背包</t>
   </si>
   <si>
-    <t>Bag</t>
-  </si>
-  <si>
     <t>equip</t>
   </si>
   <si>
     <t>裝備</t>
   </si>
   <si>
-    <t>Equip</t>
-  </si>
-  <si>
     <t>other</t>
   </si>
   <si>
     <t>其他</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>storage</t>
   </si>
   <si>
     <t>儲量</t>
   </si>
   <si>
-    <t>Storage</t>
-  </si>
-  <si>
     <t>endurance</t>
   </si>
   <si>
     <t>耐久</t>
   </si>
   <si>
-    <t>Endurance</t>
-  </si>
-  <si>
     <t>durability</t>
   </si>
   <si>
-    <t>Durability</t>
-  </si>
-  <si>
     <t>times</t>
   </si>
   <si>
     <t>次數</t>
   </si>
   <si>
-    <t>Times</t>
-  </si>
-  <si>
     <t>capacity</t>
   </si>
   <si>
     <t>容量</t>
   </si>
   <si>
-    <t>Capacity</t>
-  </si>
-  <si>
     <t>attrs</t>
   </si>
   <si>
     <t>屬性</t>
   </si>
   <si>
-    <t>Attrs</t>
-  </si>
-  <si>
     <t>states</t>
   </si>
   <si>
     <t>狀態</t>
-  </si>
-  <si>
-    <t>States</t>
   </si>
   <si>
     <t>life</t>
@@ -245,9 +176,6 @@
 降到 0，就死亡</t>
   </si>
   <si>
-    <t>Life</t>
-  </si>
-  <si>
     <t>attack</t>
   </si>
   <si>
@@ -266,156 +194,102 @@
     <t>可吸收的傷害</t>
   </si>
   <si>
-    <t>Defense</t>
-  </si>
-  <si>
     <t>use</t>
   </si>
   <si>
     <t>使用</t>
   </si>
   <si>
-    <t>Use</t>
-  </si>
-  <si>
     <t>drop</t>
   </si>
   <si>
     <t>丟棄</t>
   </si>
   <si>
-    <t>Drop</t>
-  </si>
-  <si>
     <t>take</t>
   </si>
   <si>
     <t>拿</t>
   </si>
   <si>
-    <t>Take</t>
-  </si>
-  <si>
     <t>talk</t>
   </si>
   <si>
     <t>交談</t>
   </si>
   <si>
-    <t>Talk</t>
-  </si>
-  <si>
     <t>trade</t>
   </si>
   <si>
     <t>交易</t>
   </si>
   <si>
-    <t>Trade</t>
-  </si>
-  <si>
     <t>buy</t>
   </si>
   <si>
     <t>買</t>
   </si>
   <si>
-    <t>Buy</t>
-  </si>
-  <si>
     <t>sell</t>
   </si>
   <si>
     <t>賣</t>
   </si>
   <si>
-    <t>Sell</t>
-  </si>
-  <si>
     <t>split</t>
   </si>
   <si>
     <t>拆分</t>
   </si>
   <si>
-    <t>Split</t>
-  </si>
-  <si>
     <t>open</t>
   </si>
   <si>
     <t>開啟</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>observe</t>
   </si>
   <si>
     <t>觀察</t>
   </si>
   <si>
-    <t>Observe</t>
-  </si>
-  <si>
     <t>transfer</t>
   </si>
   <si>
     <t>移動</t>
   </si>
   <si>
-    <t>Transfer</t>
-  </si>
-  <si>
     <t>openbag</t>
   </si>
   <si>
-    <t>Openbag</t>
-  </si>
-  <si>
     <t>inv</t>
   </si>
   <si>
-    <t>Inv</t>
-  </si>
-  <si>
     <t>profile</t>
   </si>
   <si>
     <t>個人</t>
   </si>
   <si>
-    <t>Profile</t>
-  </si>
-  <si>
     <t>drink</t>
   </si>
   <si>
     <t>喝水</t>
   </si>
   <si>
-    <t>Drink</t>
-  </si>
-  <si>
     <t>fill</t>
   </si>
   <si>
     <t>取水</t>
   </si>
   <si>
-    <t>Fill</t>
-  </si>
-  <si>
     <t>cook</t>
   </si>
   <si>
     <t>烹煮</t>
   </si>
   <si>
-    <t>Cook</t>
-  </si>
-  <si>
     <t>open_door</t>
   </si>
   <si>
@@ -428,198 +302,132 @@
     <t>關閉</t>
   </si>
   <si>
-    <t>Close</t>
-  </si>
-  <si>
     <t>make</t>
   </si>
   <si>
     <t>製作</t>
   </si>
   <si>
-    <t>Make</t>
-  </si>
-  <si>
     <t>rest</t>
   </si>
   <si>
     <t>休息</t>
   </si>
   <si>
-    <t>Rest</t>
-  </si>
-  <si>
     <t>wake</t>
   </si>
   <si>
     <t>起床</t>
   </si>
   <si>
-    <t>Wake</t>
-  </si>
-  <si>
     <t>setting</t>
   </si>
   <si>
     <t>設定</t>
   </si>
   <si>
-    <t>Setting</t>
-  </si>
-  <si>
     <t>_space_full</t>
   </si>
   <si>
     <t>空間已滿 !!!</t>
   </si>
   <si>
-    <t>Space is full !!!</t>
-  </si>
-  <si>
     <t>_not_enough_gold</t>
   </si>
   <si>
     <t>金幣不足 !!!</t>
   </si>
   <si>
-    <t>Not enough coins !!!</t>
-  </si>
-  <si>
     <t>iron</t>
   </si>
   <si>
     <t>鐵礦</t>
   </si>
   <si>
-    <t>Iron ore</t>
-  </si>
-  <si>
     <t>salt</t>
   </si>
   <si>
     <t>鹽</t>
   </si>
   <si>
-    <t>Salt</t>
-  </si>
-  <si>
     <t>raw_meat</t>
   </si>
   <si>
     <t>生肉</t>
   </si>
   <si>
-    <t>Raw meat</t>
-  </si>
-  <si>
     <t>cooked_meat</t>
   </si>
   <si>
     <t>熟肉</t>
   </si>
   <si>
-    <t>Cooked meat</t>
-  </si>
-  <si>
     <t>raw_fish</t>
   </si>
   <si>
     <t>生魚</t>
   </si>
   <si>
-    <t>Raw fish</t>
-  </si>
-  <si>
     <t>salt_baked_fish</t>
   </si>
   <si>
     <t>鹽烤魚</t>
   </si>
   <si>
-    <t>Salt-baked fish</t>
-  </si>
-  <si>
     <t>sword_01</t>
   </si>
   <si>
     <t>普通刀</t>
   </si>
   <si>
-    <t>Ordinary knife</t>
-  </si>
-  <si>
     <t>sword_02</t>
   </si>
   <si>
     <t>鐵劍</t>
   </si>
   <si>
-    <t>Iron Sword</t>
-  </si>
-  <si>
     <t>sword_03</t>
   </si>
   <si>
     <t>鋼劍</t>
   </si>
   <si>
-    <t>Steel Sword</t>
-  </si>
-  <si>
     <t>helmet_01</t>
   </si>
   <si>
     <t>草帽</t>
   </si>
   <si>
-    <t>Straw hat</t>
-  </si>
-  <si>
     <t>helmet_02</t>
   </si>
   <si>
     <t>麻布帽</t>
   </si>
   <si>
-    <t>Linen hat</t>
-  </si>
-  <si>
     <t>helmet_03</t>
   </si>
   <si>
     <t>皮帽</t>
   </si>
   <si>
-    <t>Leather hat</t>
-  </si>
-  <si>
     <t>chest_01</t>
   </si>
   <si>
     <t>草衣</t>
   </si>
   <si>
-    <t>Grass Clothes</t>
-  </si>
-  <si>
     <t>chest_02</t>
   </si>
   <si>
     <t>麻布衣</t>
   </si>
   <si>
-    <t>Linen Clothes</t>
-  </si>
-  <si>
     <t>chest_03</t>
   </si>
   <si>
     <t>皮衣</t>
   </si>
   <si>
-    <t>Leather</t>
-  </si>
-  <si>
     <t>gloves_01</t>
   </si>
   <si>
@@ -638,18 +446,12 @@
     <t>火把</t>
   </si>
   <si>
-    <t>Torch</t>
-  </si>
-  <si>
     <t>bottle</t>
   </si>
   <si>
     <t>水壺</t>
   </si>
   <si>
-    <t>Bottle</t>
-  </si>
-  <si>
     <t>wick</t>
   </si>
   <si>
@@ -659,9 +461,6 @@
     <t>冒險者</t>
   </si>
   <si>
-    <t>Wick</t>
-  </si>
-  <si>
     <t>dummy</t>
   </si>
   <si>
@@ -671,9 +470,6 @@
     <t>練習攻擊用</t>
   </si>
   <si>
-    <t>Training Dummy</t>
-  </si>
-  <si>
     <t>musk</t>
   </si>
   <si>
@@ -683,9 +479,6 @@
     <t>寡言卻可靠的中年壯漢，鍛造技術一流，據說曾是王都兵工坊的首席</t>
   </si>
   <si>
-    <t>Musk</t>
-  </si>
-  <si>
     <t>trump</t>
   </si>
   <si>
@@ -695,9 +488,6 @@
     <t>胖胖和氣的大叔，愛講笑話和八卦，是村裡的情報中心。</t>
   </si>
   <si>
-    <t>Trump</t>
-  </si>
-  <si>
     <t>karen</t>
   </si>
   <si>
@@ -707,9 +497,6 @@
     <t>每天從村外的田地或森林帶回最新鮮的農作物，推著小車叫賣，聲音又甜又響亮～</t>
   </si>
   <si>
-    <t>Gilly</t>
-  </si>
-  <si>
     <t>xi</t>
   </si>
   <si>
@@ -719,9 +506,6 @@
     <t>負責村裡所有牲畜的宰殺與肉品加工。據說他手起刀落，比鐵匠還俐落……</t>
   </si>
   <si>
-    <t>Xi Jinping</t>
-  </si>
-  <si>
     <t>macron</t>
   </si>
   <si>
@@ -731,9 +515,6 @@
     <t>矮個子滿臉皺紋的小老頭，總能拿出些「你不知道自己需要的東西」。</t>
   </si>
   <si>
-    <t>Macron</t>
-  </si>
-  <si>
     <t>melanie</t>
   </si>
   <si>
@@ -743,9 +524,6 @@
     <t>漂亮大方的女士，跟川普共同經營一家旅館</t>
   </si>
   <si>
-    <t>Melanie</t>
-  </si>
-  <si>
     <t>rogue</t>
   </si>
   <si>
@@ -761,9 +539,6 @@
     <t>駐守南門的守衛，跟搭檔輪流日夜巡邏村子</t>
   </si>
   <si>
-    <t>Guard</t>
-  </si>
-  <si>
     <t>guard-2</t>
   </si>
   <si>
@@ -776,9 +551,6 @@
     <t>弓箭高手、森林獵人、野外生存達人，腳步輕盈如風，氣息比幽靈還難察覺</t>
   </si>
   <si>
-    <t>Ranger</t>
-  </si>
-  <si>
     <t>smith</t>
   </si>
   <si>
@@ -788,9 +560,6 @@
     <t>打造武器、防具與工具的鍛造高手。</t>
   </si>
   <si>
-    <t>Smith</t>
-  </si>
-  <si>
     <t>innkeeper</t>
   </si>
   <si>
@@ -800,9 +569,6 @@
     <t>經營旅館與酒館，消息靈通的熱情招待。</t>
   </si>
   <si>
-    <t>Innkeeper</t>
-  </si>
-  <si>
     <t>trader</t>
   </si>
   <si>
@@ -812,9 +578,6 @@
     <t>村內攤商，賣日用品或冒險裝備。</t>
   </si>
   <si>
-    <t>Trader</t>
-  </si>
-  <si>
     <t>butcher</t>
   </si>
   <si>
@@ -824,9 +587,6 @@
     <t>處理牲畜肉品，刀法俐落，力氣驚人。</t>
   </si>
   <si>
-    <t>Butcher</t>
-  </si>
-  <si>
     <t>merchant</t>
   </si>
   <si>
@@ -834,9 +594,6 @@
   </si>
   <si>
     <t>來去自如的商旅，販售異地貨品。</t>
-  </si>
-  <si>
-    <t>Merchant</t>
   </si>
   <si>
     <t>guard</t>
@@ -1333,27 +1090,18 @@
     <t>拾取</t>
   </si>
   <si>
-    <t>Pickup</t>
-  </si>
-  <si>
     <t>lock</t>
   </si>
   <si>
     <t>上鎖</t>
   </si>
   <si>
-    <t>Lock</t>
-  </si>
-  <si>
     <t>unlock</t>
   </si>
   <si>
     <t>解鎖</t>
   </si>
   <si>
-    <t>Unlock</t>
-  </si>
-  <si>
     <t>解剖</t>
   </si>
   <si>
@@ -1361,9 +1109,6 @@
   </si>
   <si>
     <t>恢復</t>
-  </si>
-  <si>
-    <t>Restore</t>
   </si>
 </sst>
 </file>
@@ -1832,590 +1577,535 @@
     <col min="6" max="16384" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="26" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="B41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="B42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>152</v>
-      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2436,220 +2126,198 @@
     <col min="6" max="16384" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>433</v>
+        <v>352</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>436</v>
+        <v>354</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>442</v>
+        <v>358</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>443</v>
+        <v>359</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>444</v>
+        <v>360</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="3" t="s">
-        <v>445</v>
-      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2668,299 +2336,272 @@
     <col min="5" max="5" width="11.125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>43</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>170</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>179</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>188</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="D19" s="8"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>192</v>
+        <v>130</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>197</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>34</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>40</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>207</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2980,142 +2621,129 @@
     <col min="5" max="5" width="11.125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>213</v>
+        <v>146</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>220</v>
+        <v>151</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>224</v>
+        <v>154</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>225</v>
+        <v>155</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>232</v>
+        <v>160</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>239</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
@@ -3123,10 +2751,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>240</v>
+        <v>166</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>241</v>
+        <v>167</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="8"/>
@@ -3134,32 +2762,28 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>245</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D13" s="8"/>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>245</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D14" s="8"/>
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3249,133 +2873,119 @@
     <col min="6" max="16384" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>251</v>
+        <v>175</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>252</v>
+        <v>176</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>266</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>267</v>
+        <v>187</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>268</v>
+        <v>188</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>270</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="D9" s="13"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>271</v>
+        <v>190</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>245</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="D10" s="13"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3488,503 +3098,589 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>192</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>277</v>
+        <v>196</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>283</v>
+        <v>202</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>287</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="C9" s="18"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>297</v>
+        <v>216</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>298</v>
+        <v>217</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>304</v>
+        <v>223</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>306</v>
+        <v>225</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>311</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>312</v>
+        <v>231</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>313</v>
+        <v>232</v>
       </c>
       <c r="C19" s="18"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>314</v>
+        <v>233</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>315</v>
+        <v>234</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>317</v>
+        <v>236</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>321</v>
+        <v>240</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>323</v>
+        <v>242</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>324</v>
+        <v>243</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>325</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="C25" s="18"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>328</v>
+        <v>247</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>329</v>
+        <v>248</v>
       </c>
       <c r="C26" s="18"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>330</v>
+        <v>249</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>331</v>
+        <v>250</v>
       </c>
       <c r="C27" s="18"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>332</v>
+        <v>251</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>333</v>
+        <v>252</v>
       </c>
       <c r="C28" s="18"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c r="C29" s="18"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
     </row>
-    <row r="31" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>336</v>
+        <v>255</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>337</v>
+        <v>256</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>338</v>
+        <v>257</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="33" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>340</v>
+        <v>259</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>341</v>
+        <v>260</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>342</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>343</v>
+        <v>262</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>344</v>
+        <v>263</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>346</v>
+        <v>265</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>347</v>
+        <v>266</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>344</v>
+        <v>263</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>354</v>
+        <v>273</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>347</v>
+        <v>266</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>360</v>
+        <v>279</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>362</v>
+        <v>281</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C49" s="4"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C53" s="4"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>380</v>
+        <v>299</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>382</v>
+        <v>301</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>383</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4009,49 +3705,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>4</v>
-      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>384</v>
+        <v>303</v>
       </c>
       <c r="B4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>386</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>388</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -4079,76 +3769,80 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>4</v>
-      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>390</v>
+        <v>309</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>394</v>
+        <v>313</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>377</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>396</v>
+        <v>315</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>397</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>398</v>
+        <v>317</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>399</v>
+        <v>318</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4163,10 +3857,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>400</v>
+        <v>319</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>401</v>
+        <v>320</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4174,10 +3868,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>402</v>
+        <v>321</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>403</v>
+        <v>322</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4185,10 +3879,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>404</v>
+        <v>323</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4221,66 +3915,70 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>4</v>
-      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>408</v>
+        <v>327</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>410</v>
+        <v>329</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>414</v>
+        <v>333</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>415</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4303,96 +4001,90 @@
         <v>1</v>
       </c>
       <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>416</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>337</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>420</v>
+        <v>339</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>422</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>424</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>345</v>
       </c>
       <c r="B8" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>428</v>
+        <v>347</v>
       </c>
       <c r="B9" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>430</v>
+        <v>349</v>
       </c>
       <c r="B10" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>431</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
-        <v>432</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -17,13 +17,14 @@
     <sheet sheetId="8" name="quest" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="ability" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="option" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="msg" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="489">
   <si>
     <t>key</t>
   </si>
@@ -338,6 +339,132 @@
     <t>金幣不足 !!!</t>
   </si>
   <si>
+    <t>player</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>quest_general</t>
+  </si>
+  <si>
+    <t>一般任務</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>說明</t>
+  </si>
+  <si>
+    <t>progress</t>
+  </si>
+  <si>
+    <t>進度</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+  <si>
+    <t>清除</t>
+  </si>
+  <si>
+    <t>select_all</t>
+  </si>
+  <si>
+    <t>全選</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>送出</t>
+  </si>
+  <si>
+    <t>save</t>
+  </si>
+  <si>
+    <t>存檔</t>
+  </si>
+  <si>
+    <t>leave</t>
+  </si>
+  <si>
+    <t>離開</t>
+  </si>
+  <si>
+    <t>mode_toggle</t>
+  </si>
+  <si>
+    <t>模式:{#v}</t>
+  </si>
+  <si>
+    <t>manufacture</t>
+  </si>
+  <si>
+    <t>製造</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>地圖</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>主要</t>
+  </si>
+  <si>
+    <t>mouse_edge_move</t>
+  </si>
+  <si>
+    <t>滑鼠移動到邊緣可移動鏡頭</t>
+  </si>
+  <si>
+    <t>pointer_lock</t>
+  </si>
+  <si>
+    <t>滑鼠鎖定模式</t>
+  </si>
+  <si>
+    <t>start_game</t>
+  </si>
+  <si>
+    <t>開始遊戲</t>
+  </si>
+  <si>
+    <t>game_setting</t>
+  </si>
+  <si>
+    <t>遊戲設定</t>
+  </si>
+  <si>
+    <t>map_show_names</t>
+  </si>
+  <si>
+    <t>顯示地名</t>
+  </si>
+  <si>
+    <t>map_show_quests</t>
+  </si>
+  <si>
+    <t>顯示任務</t>
+  </si>
+  <si>
     <t>iron</t>
   </si>
   <si>
@@ -1109,6 +1236,265 @@
   </si>
   <si>
     <t>恢復</t>
+  </si>
+  <si>
+    <t>_beg_mercy</t>
+  </si>
+  <si>
+    <t>不要殺我!!!</t>
+  </si>
+  <si>
+    <t>_shout_help</t>
+  </si>
+  <si>
+    <t>救命啊！</t>
+  </si>
+  <si>
+    <t>_shout_come</t>
+  </si>
+  <si>
+    <t>來人啊！</t>
+  </si>
+  <si>
+    <t>_shout_murder</t>
+  </si>
+  <si>
+    <t>有人要殺我！</t>
+  </si>
+  <si>
+    <t>_harvest_need_tool</t>
+  </si>
+  <si>
+    <t>需要 {#tool} 才能採集</t>
+  </si>
+  <si>
+    <t>_harvest_chop</t>
+  </si>
+  <si>
+    <t>砍了 {#cur}/{#max} 下</t>
+  </si>
+  <si>
+    <t>_harvest_drop</t>
+  </si>
+  <si>
+    <t>掉落 {#item} x{#count}</t>
+  </si>
+  <si>
+    <t>_harvest_get</t>
+  </si>
+  <si>
+    <t>獲得 {#item}</t>
+  </si>
+  <si>
+    <t>_lock_no_skill</t>
+  </si>
+  <si>
+    <t>缺少開鎖技能</t>
+  </si>
+  <si>
+    <t>_lock_no_tool</t>
+  </si>
+  <si>
+    <t>缺少開鎖工具</t>
+  </si>
+  <si>
+    <t>_lock_confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用開鎖工具開鎖？
+成功率 {#rate}%</t>
+  </si>
+  <si>
+    <t>_lock_fail</t>
+  </si>
+  <si>
+    <t>{#who} 開鎖失敗</t>
+  </si>
+  <si>
+    <t>_lock_tool_broken</t>
+  </si>
+  <si>
+    <t>開鎖工具損壞了</t>
+  </si>
+  <si>
+    <t>_lock_locked</t>
+  </si>
+  <si>
+    <t>{#who} 上鎖</t>
+  </si>
+  <si>
+    <t>_lock_unlocked</t>
+  </si>
+  <si>
+    <t>{#who} 開鎖</t>
+  </si>
+  <si>
+    <t>_loot_no_knife</t>
+  </si>
+  <si>
+    <t>沒有刀具，無法解剖</t>
+  </si>
+  <si>
+    <t>_loot_get</t>
+  </si>
+  <si>
+    <t>{#who} 獲得 {#item}</t>
+  </si>
+  <si>
+    <t>_hunger</t>
+  </si>
+  <si>
+    <t>{#who} {#pct}% 飢餓</t>
+  </si>
+  <si>
+    <t>_thirst</t>
+  </si>
+  <si>
+    <t>{#who} {#pct}% 口渴</t>
+  </si>
+  <si>
+    <t>_steal_ok</t>
+  </si>
+  <si>
+    <t>{#who} 成功偷竊 {#item}</t>
+  </si>
+  <si>
+    <t>_steal_fail</t>
+  </si>
+  <si>
+    <t>{#who} 偷竊失敗</t>
+  </si>
+  <si>
+    <t>_steal_confirm</t>
+  </si>
+  <si>
+    <t>偷竊嗎?</t>
+  </si>
+  <si>
+    <t>_trade_refuse</t>
+  </si>
+  <si>
+    <t>無法交易</t>
+  </si>
+  <si>
+    <t>_fill_water</t>
+  </si>
+  <si>
+    <t>{#who} 裝水</t>
+  </si>
+  <si>
+    <t>_bottle_full</t>
+  </si>
+  <si>
+    <t>{#who} 水壺已滿</t>
+  </si>
+  <si>
+    <t>_learn_confirm</t>
+  </si>
+  <si>
+    <t>學習此技能?</t>
+  </si>
+  <si>
+    <t>_quest_updated</t>
+  </si>
+  <si>
+    <t>更新任務</t>
+  </si>
+  <si>
+    <t>_dlg_hint</t>
+  </si>
+  <si>
+    <t>（{#hint}）</t>
+  </si>
+  <si>
+    <t>_dlg_listen</t>
+  </si>
+  <si>
+    <t>*聆聽...*</t>
+  </si>
+  <si>
+    <t>_favor_value</t>
+  </si>
+  <si>
+    <t>好感 : {#v}</t>
+  </si>
+  <si>
+    <t>_eff_stage</t>
+  </si>
+  <si>
+    <t>{#v}時，</t>
+  </si>
+  <si>
+    <t>_eff_trigger</t>
+  </si>
+  <si>
+    <t>觸發[color=skyblue]{#v}[/color]，</t>
+  </si>
+  <si>
+    <t>_eff_trigger_end</t>
+  </si>
+  <si>
+    <t>觸發[color=skyblue]{#v}[/color]</t>
+  </si>
+  <si>
+    <t>_eff_dur</t>
+  </si>
+  <si>
+    <t>，持續[color=white]{#v}[/color]回合</t>
+  </si>
+  <si>
+    <t>_eff_stack</t>
+  </si>
+  <si>
+    <t>，最多疊加[color=white]{#v}[/color]層</t>
+  </si>
+  <si>
+    <t>_eff_dot</t>
+  </si>
+  <si>
+    <t>{#stage}{#scope}{#trigger}每回合{#num}血量{#dur}{#stack}</t>
+  </si>
+  <si>
+    <t>_eff_buff</t>
+  </si>
+  <si>
+    <t>{#stage}{#scope}{#trigger}{#key}{#num}{#dur}{#stack}</t>
+  </si>
+  <si>
+    <t>_eff_mod</t>
+  </si>
+  <si>
+    <t>{#stage}{#scope}{#key}{#num}</t>
+  </si>
+  <si>
+    <t>_eff_action</t>
+  </si>
+  <si>
+    <t>{#stage}{#trigger}{#des}</t>
+  </si>
+  <si>
+    <t>_active_dot</t>
+  </si>
+  <si>
+    <t>每回合{#num}血量</t>
+  </si>
+  <si>
+    <t>_active_buff_key</t>
+  </si>
+  <si>
+    <t>有效回合內，{#key}{#num}</t>
+  </si>
+  <si>
+    <t>_active_buff</t>
+  </si>
+  <si>
+    <t>有效回合內，{#id}</t>
+  </si>
+  <si>
+    <t>_active_remaining</t>
+  </si>
+  <si>
+    <t>{#eff}，剩[color=white]{#n}[/color]回合</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.375" style="1" customWidth="1"/>
@@ -1584,6 +1970,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
@@ -2106,6 +2493,195 @@
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2269,40 +2845,40 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>355</v>
+        <v>397</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>356</v>
+        <v>398</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3"/>
@@ -2310,10 +2886,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
@@ -2321,6 +2897,433 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24.375" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="50.25" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="5" max="5" width="12.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C45" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -2358,20 +3361,20 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -2391,40 +3394,40 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="6"/>
@@ -2435,30 +3438,30 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="6"/>
@@ -2469,30 +3472,30 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="6"/>
@@ -2503,30 +3506,30 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="6"/>
@@ -2537,7 +3540,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>21</v>
@@ -2547,7 +3550,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>23</v>
@@ -2561,7 +3564,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>25</v>
@@ -2571,7 +3574,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>27</v>
@@ -2585,20 +3588,20 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="6"/>
@@ -2643,104 +3646,104 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="6"/>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="6"/>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="6"/>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="6"/>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="6"/>
@@ -2751,10 +3754,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="8"/>
@@ -2762,26 +3765,26 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="6"/>
@@ -2896,13 +3899,13 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -2912,78 +3915,78 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="3"/>
@@ -3114,65 +4117,65 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -3183,10 +4186,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="3"/>
@@ -3194,104 +4197,104 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>54</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>220</v>
+        <v>262</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>221</v>
+        <v>263</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -3302,10 +4305,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="3"/>
@@ -3313,52 +4316,52 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -3369,10 +4372,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="3"/>
@@ -3380,10 +4383,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="3"/>
@@ -3391,10 +4394,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="3"/>
@@ -3402,10 +4405,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="3"/>
@@ -3413,10 +4416,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="3"/>
@@ -3428,7 +4431,7 @@
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>48</v>
@@ -3441,26 +4444,26 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -3471,138 +4474,138 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>264</v>
+        <v>306</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>279</v>
+        <v>321</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="3"/>
@@ -3610,33 +4613,33 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="3"/>
@@ -3644,40 +4647,40 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>295</v>
+        <v>337</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>297</v>
+        <v>339</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>298</v>
+        <v>340</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3720,28 +4723,28 @@
       <c r="E2" s="16"/>
     </row>
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>307</v>
+        <v>349</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -3786,20 +4789,20 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>309</v>
+        <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -3816,33 +4819,33 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>313</v>
+        <v>355</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>314</v>
+        <v>356</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -3857,10 +4860,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -3868,10 +4871,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>322</v>
+        <v>364</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -3879,10 +4882,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -3932,50 +4935,50 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>326</v>
+        <v>368</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>327</v>
+        <v>369</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>329</v>
+        <v>371</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -4015,76 +5018,76 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>335</v>
+        <v>377</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="B6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="B7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="B9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="B10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="B12" t="s">
-        <v>351</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="497">
   <si>
     <t>key</t>
   </si>
@@ -1495,6 +1495,30 @@
   </si>
   <si>
     <t>{#eff}，剩[color=white]{#n}[/color]回合</t>
+  </si>
+  <si>
+    <t>_trade_sell</t>
+  </si>
+  <si>
+    <t>[weight=900]{#who}[/weight] 賣 {#item}</t>
+  </si>
+  <si>
+    <t>_trade_buy</t>
+  </si>
+  <si>
+    <t>[weight=900]{#who}[/weight] 買 {#item}</t>
+  </si>
+  <si>
+    <t>_drop_item</t>
+  </si>
+  <si>
+    <t>丟棄 {#item}</t>
+  </si>
+  <si>
+    <t>_pickup_item</t>
+  </si>
+  <si>
+    <t>拾取 {#item}</t>
   </si>
 </sst>
 </file>
@@ -2902,7 +2926,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24.375" customWidth="1"/>
@@ -3321,9 +3345,41 @@
       </c>
       <c r="C45" s="2"/>
     </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>489</v>
+      </c>
+      <c r="B46" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>491</v>
+      </c>
+      <c r="B47" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>493</v>
+      </c>
+      <c r="B48" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>495</v>
+      </c>
+      <c r="B49" t="s">
+        <v>496</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="505">
   <si>
     <t>key</t>
   </si>
@@ -667,6 +667,30 @@
   </si>
   <si>
     <t>guard-2</t>
+  </si>
+  <si>
+    <t>rogue-1</t>
+  </si>
+  <si>
+    <t>rogue-2</t>
+  </si>
+  <si>
+    <t>orc</t>
+  </si>
+  <si>
+    <t>獸人</t>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>狼</t>
+  </si>
+  <si>
+    <t>horse</t>
+  </si>
+  <si>
+    <t>馬</t>
   </si>
   <si>
     <t>ranger</t>
@@ -2869,40 +2893,40 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3"/>
@@ -2910,10 +2934,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
@@ -2960,421 +2984,421 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C44" s="2"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B46" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B47" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B48" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B49" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -3846,23 +3870,53 @@
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="9"/>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="9"/>
       <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="9"/>
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" s="9"/>
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="9"/>
       <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3955,13 +4009,13 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -3971,78 +4025,78 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>211</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="3"/>
@@ -4173,65 +4227,65 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4242,10 +4296,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="3"/>
@@ -4253,104 +4307,104 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>54</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -4361,10 +4415,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="3"/>
@@ -4372,52 +4426,52 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -4428,10 +4482,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="3"/>
@@ -4439,10 +4493,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="3"/>
@@ -4450,10 +4504,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="3"/>
@@ -4461,10 +4515,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="3"/>
@@ -4472,10 +4526,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="3"/>
@@ -4487,7 +4541,7 @@
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>48</v>
@@ -4500,26 +4554,26 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -4530,138 +4584,138 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B39" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>305</v>
-      </c>
       <c r="C39" s="19" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="3"/>
@@ -4669,33 +4723,33 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="3"/>
@@ -4703,40 +4757,40 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -4781,26 +4835,26 @@
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B4" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -4845,20 +4899,20 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -4875,33 +4929,33 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4916,10 +4970,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4927,10 +4981,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4938,10 +4992,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4991,50 +5045,50 @@
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -5076,74 +5130,74 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B4" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B5" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B6" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B7" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B8" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B9" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B10" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B12" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -9,22 +9,21 @@
   <sheets>
     <sheet sheetId="1" name="general" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="items" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="roles" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="jobs" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="stat" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="tag" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="other" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="quest" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="ability" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="option" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="msg" state="visible" r:id="rId14"/>
+    <sheet sheetId="4" name="jobs" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="stat" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="tag" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="other" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="quest" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="ability" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="option" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="msg" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="470">
   <si>
     <t>key</t>
   </si>
@@ -579,178 +578,73 @@
     <t>水壺</t>
   </si>
   <si>
-    <t>wick</t>
-  </si>
-  <si>
-    <t>維克</t>
-  </si>
-  <si>
-    <t>冒險者</t>
-  </si>
-  <si>
-    <t>dummy</t>
-  </si>
-  <si>
-    <t>木樁</t>
-  </si>
-  <si>
-    <t>練習攻擊用</t>
-  </si>
-  <si>
-    <t>musk</t>
-  </si>
-  <si>
-    <t>馬斯克</t>
-  </si>
-  <si>
-    <t>寡言卻可靠的中年壯漢，鍛造技術一流，據說曾是王都兵工坊的首席</t>
-  </si>
-  <si>
-    <t>trump</t>
-  </si>
-  <si>
-    <t>川普</t>
-  </si>
-  <si>
-    <t>胖胖和氣的大叔，愛講笑話和八卦，是村裡的情報中心。</t>
-  </si>
-  <si>
-    <t>karen</t>
-  </si>
-  <si>
-    <t>凱倫</t>
-  </si>
-  <si>
-    <t>每天從村外的田地或森林帶回最新鮮的農作物，推著小車叫賣，聲音又甜又響亮～</t>
-  </si>
-  <si>
-    <t>xi</t>
-  </si>
-  <si>
-    <t>習近平</t>
-  </si>
-  <si>
-    <t>負責村裡所有牲畜的宰殺與肉品加工。據說他手起刀落，比鐵匠還俐落……</t>
-  </si>
-  <si>
-    <t>macron</t>
-  </si>
-  <si>
-    <t>馬克宏</t>
-  </si>
-  <si>
-    <t>矮個子滿臉皺紋的小老頭，總能拿出些「你不知道自己需要的東西」。</t>
-  </si>
-  <si>
-    <t>melanie</t>
-  </si>
-  <si>
-    <t>梅蘭妮</t>
-  </si>
-  <si>
-    <t>漂亮大方的女士，跟川普共同經營一家旅館</t>
+    <t>ranger</t>
+  </si>
+  <si>
+    <t>遊俠</t>
+  </si>
+  <si>
+    <t>弓箭高手、森林獵人、野外生存達人，腳步輕盈如風，氣息比幽靈還難察覺</t>
+  </si>
+  <si>
+    <t>smith</t>
+  </si>
+  <si>
+    <t>鐵匠</t>
+  </si>
+  <si>
+    <t>打造武器、防具與工具的鍛造高手。</t>
+  </si>
+  <si>
+    <t>innkeeper</t>
+  </si>
+  <si>
+    <t>旅館老闆</t>
+  </si>
+  <si>
+    <t>經營旅館與酒館，消息靈通的熱情招待。</t>
+  </si>
+  <si>
+    <t>trader</t>
+  </si>
+  <si>
+    <t>小販</t>
+  </si>
+  <si>
+    <t>村內攤商，賣日用品或冒險裝備。</t>
+  </si>
+  <si>
+    <t>butcher</t>
+  </si>
+  <si>
+    <t>屠夫</t>
+  </si>
+  <si>
+    <t>處理牲畜肉品，刀法俐落，力氣驚人。</t>
+  </si>
+  <si>
+    <t>merchant</t>
+  </si>
+  <si>
+    <t>行商</t>
+  </si>
+  <si>
+    <t>來去自如的商旅，販售異地貨品。</t>
+  </si>
+  <si>
+    <t>guard</t>
+  </si>
+  <si>
+    <t>守衛</t>
+  </si>
+  <si>
+    <t>巡邏村莊、維持治安。</t>
   </si>
   <si>
     <t>rogue</t>
   </si>
   <si>
     <t>盜賊</t>
-  </si>
-  <si>
-    <t>guard-1</t>
-  </si>
-  <si>
-    <t>守衛</t>
-  </si>
-  <si>
-    <t>駐守南門的守衛，跟搭檔輪流日夜巡邏村子</t>
-  </si>
-  <si>
-    <t>guard-2</t>
-  </si>
-  <si>
-    <t>rogue-1</t>
-  </si>
-  <si>
-    <t>rogue-2</t>
-  </si>
-  <si>
-    <t>orc</t>
-  </si>
-  <si>
-    <t>獸人</t>
-  </si>
-  <si>
-    <t>wolf</t>
-  </si>
-  <si>
-    <t>狼</t>
-  </si>
-  <si>
-    <t>horse</t>
-  </si>
-  <si>
-    <t>馬</t>
-  </si>
-  <si>
-    <t>ranger</t>
-  </si>
-  <si>
-    <t>遊俠</t>
-  </si>
-  <si>
-    <t>弓箭高手、森林獵人、野外生存達人，腳步輕盈如風，氣息比幽靈還難察覺</t>
-  </si>
-  <si>
-    <t>smith</t>
-  </si>
-  <si>
-    <t>鐵匠</t>
-  </si>
-  <si>
-    <t>打造武器、防具與工具的鍛造高手。</t>
-  </si>
-  <si>
-    <t>innkeeper</t>
-  </si>
-  <si>
-    <t>旅館老闆</t>
-  </si>
-  <si>
-    <t>經營旅館與酒館，消息靈通的熱情招待。</t>
-  </si>
-  <si>
-    <t>trader</t>
-  </si>
-  <si>
-    <t>小販</t>
-  </si>
-  <si>
-    <t>村內攤商，賣日用品或冒險裝備。</t>
-  </si>
-  <si>
-    <t>butcher</t>
-  </si>
-  <si>
-    <t>屠夫</t>
-  </si>
-  <si>
-    <t>處理牲畜肉品，刀法俐落，力氣驚人。</t>
-  </si>
-  <si>
-    <t>merchant</t>
-  </si>
-  <si>
-    <t>行商</t>
-  </si>
-  <si>
-    <t>來去自如的商旅，販售異地貨品。</t>
-  </si>
-  <si>
-    <t>guard</t>
-  </si>
-  <si>
-    <t>巡邏村莊、維持治安。</t>
   </si>
   <si>
     <t>str</t>
@@ -1639,7 +1533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1664,9 +1558,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2893,40 +2784,40 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>404</v>
+        <v>369</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>406</v>
+        <v>371</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3"/>
@@ -2934,10 +2825,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
@@ -2984,421 +2875,421 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>412</v>
+        <v>377</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>413</v>
+        <v>378</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>414</v>
+        <v>379</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>415</v>
+        <v>380</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>416</v>
+        <v>381</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>417</v>
+        <v>382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>418</v>
+        <v>383</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>421</v>
+        <v>386</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>424</v>
+        <v>389</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>425</v>
+        <v>390</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>433</v>
+        <v>398</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>440</v>
+        <v>405</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>448</v>
+        <v>413</v>
       </c>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>450</v>
+        <v>415</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>456</v>
+        <v>421</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>457</v>
+        <v>422</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>461</v>
+        <v>426</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>472</v>
+        <v>437</v>
       </c>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>474</v>
+        <v>439</v>
       </c>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>476</v>
+        <v>441</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>482</v>
+        <v>447</v>
       </c>
       <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>489</v>
+        <v>454</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>490</v>
+        <v>455</v>
       </c>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>492</v>
+        <v>457</v>
       </c>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="C44" s="2"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="C45" s="2"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="B46" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="B47" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="B48" t="s">
-        <v>502</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="B49" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -3692,295 +3583,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="14.875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="42.5" style="9" customWidth="1"/>
-    <col min="4" max="4" width="19.625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" ht="33" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="D20" s="8"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="D25" s="8"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="D26" s="8"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="D31" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="42.5" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14.875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="42.5" style="10" customWidth="1"/>
     <col min="4" max="4" width="19.625" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.125" style="3" customWidth="1"/>
     <col min="6" max="16384" width="8.875" style="1" customWidth="1"/>
@@ -3990,7 +3600,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3"/>
@@ -3998,10 +3608,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="3"/>
@@ -4009,13 +3619,13 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4024,86 +3634,92 @@
       <c r="A4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="D5" s="13"/>
+      <c r="A5" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="12"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="13"/>
+      <c r="A6" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="D7" s="13"/>
+      <c r="A7" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="12"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" s="13"/>
+      <c r="A8" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="12"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="D9" s="13"/>
+      <c r="A9" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="12"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="D10" s="13"/>
+      <c r="A10" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="12"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
@@ -4215,338 +3831,338 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>244</v>
+        <v>207</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>209</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>247</v>
+        <v>210</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>212</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>250</v>
+        <v>213</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>253</v>
+        <v>216</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>256</v>
+        <v>219</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="18"/>
+        <v>222</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="17"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B10" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>260</v>
+      <c r="C10" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B11" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>262</v>
+      <c r="C11" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>265</v>
+        <v>228</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>230</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>268</v>
+        <v>231</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>233</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>271</v>
+        <v>234</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>236</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>274</v>
+        <v>237</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>277</v>
+        <v>240</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>242</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>280</v>
+        <v>243</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>245</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="C19" s="18"/>
+        <v>246</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" s="17"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>285</v>
+        <v>248</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>250</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>288</v>
+        <v>251</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>253</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>291</v>
+        <v>254</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>256</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>294</v>
+        <v>257</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>259</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C25" s="18"/>
+        <v>260</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="17"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C26" s="18"/>
+        <v>262</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="C26" s="17"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="C27" s="18"/>
+        <v>264</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" s="17"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="C28" s="18"/>
+        <v>266</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" s="17"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="C29" s="18"/>
+        <v>268</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="C29" s="17"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B31" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>49</v>
       </c>
       <c r="D31" s="3"/>
@@ -4554,168 +4170,168 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>273</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>311</v>
+        <v>274</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>276</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>314</v>
+        <v>277</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>279</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>317</v>
+        <v>280</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>282</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>320</v>
+        <v>283</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>285</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>322</v>
+        <v>286</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>287</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>324</v>
+        <v>288</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>329</v>
+        <v>294</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="3"/>
@@ -4723,33 +4339,33 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="3"/>
@@ -4757,40 +4373,40 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -4822,39 +4438,39 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="B5" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="B6" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -4886,33 +4502,33 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>361</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -4929,33 +4545,33 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4970,10 +4586,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4981,10 +4597,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>371</v>
+        <v>336</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>372</v>
+        <v>337</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4992,10 +4608,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -5032,63 +4648,63 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>376</v>
+        <v>341</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -5130,74 +4746,74 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="B3" t="s">
-        <v>386</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="B4" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="B6" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="B7" t="s">
-        <v>394</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>396</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="B9" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="B12" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
